--- a/out/川上谷川_土壌調査試料採取位置図_現場技術員所見.xlsx
+++ b/out/川上谷川_土壌調査試料採取位置図_現場技術員所見.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="120" customHeight="1">
+    <row r="8" ht="150" customHeight="1">
       <c r="A8" s="7" t="n">
         <v>1</v>
       </c>
@@ -641,24 +641,26 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>151工区内に2箇所</t>
+          <t>151工区内に2箇所
+（計3検体）</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>149工区は1箇所であるのに対し、151工区は同一工区内に2箇所（②・③）計画されているが、2箇所必要な理由が示されていない。
-②と③は地図上で離れている。浚渫範囲が2つに分かれている場合、浚渫土量が採取頻度の基準を超える場合、土質や汚染の条件（道路排水・人家からの流入等）が異なる場合などであれば妥当と考えられるが、現資料では判断できない。</t>
+          <t>151工区の浚渫範囲は2つに分かれており、受注者はそれぞれに1箇所（②・③）を計画しているが、同一工区内で2箇所必要な理由（根拠）が示されていない。
+発注者は1箇所追加（計2検体：①・③）を想定しており、受注者計画（3検体）より1検体多い。②を追加する場合は、土砂条例・受入先の採取基準（発生場所ごと、土量ごと等）により151工区の2範囲を別の発生場所として扱う必要があるか、または土質・汚染条件が異なるかの根拠が必要である。
+根拠がない場合は、151工区は③の1箇所とするか、②・③の範囲から等量採取した混合試料1検体とする方法（条例・受入先が認める場合）が考えられる。</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>・151工区で2箇所必要な理由を示すこと
-・採取箇所数の根拠（特記仕様書・受入先の条件、浚渫土量あたりの採取頻度、土質の違い等）を示すこと</t>
+          <t>・151工区で2検体とする根拠（土砂条例施行規則・受入先の採取基準、土質の違い等）を示すこと
+・根拠がない場合は、発注者想定（①・③の2検体）とするか、②・③の混合試料1検体とすることを検討すること</t>
         </is>
       </c>
       <c r="G8" s="10" t="n"/>
     </row>
-    <row r="9" ht="85" customHeight="1">
+    <row r="9" ht="80" customHeight="1">
       <c r="A9" s="7" t="n">
         <v>2</v>
       </c>
@@ -679,18 +681,18 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>149工区は浚渫範囲が着色されているが、151工区は浚渫範囲が示されていない。このため、②・③が浚渫範囲内にあるか、範囲が一連の区間か2つに分かれているかを確認できない。</t>
+          <t>149工区は浚渫範囲が着色されているが、151工区は2つに分かれた浚渫範囲が示されていない。このため、②・③がそれぞれの浚渫範囲内にあることを図上で確認できない。</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>・151工区の浚渫範囲を149工区と同様に着色して明示すること
-・②・③が浚渫範囲内にあることを図上で示すこと</t>
+          <t>・151工区の浚渫範囲（2範囲）を149工区と同様に着色して明示すること
+・各範囲の浚渫土量を示すこと</t>
         </is>
       </c>
       <c r="G9" s="10" t="n"/>
     </row>
-    <row r="10" ht="95" customHeight="1">
+    <row r="10" ht="115" customHeight="1">
       <c r="A10" s="7" t="n">
         <v>3</v>
       </c>
@@ -711,18 +713,19 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>当初設計の土壌調査の検体数・試験項目との関係が示されていない。設計が2検体（工区ごとに1検体）の場合、受注者の判断による追加となり、費用負担の扱いを確認する必要がある。設計が3検体の場合は、149に1検体、151に2検体とした配分の理由が必要である。</t>
+          <t>発注者の想定は2検体（当初1検体＋追加1検体、①・③）であり、受注者計画の3検体とは1検体の差がある。追加の1検体（②）を設計変更の対象とするかは、上記No.1の根拠次第であり、根拠が認められない場合は受注者の任意による追加（設計変更の対象外）となる旨を事前に整理しておく必要がある。
+③を151工区の代表とする場合は、③の範囲が151工区の浚渫土を代表すること（浚渫土量の大きい範囲である等）も確認しておくことが望ましい。</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>・当初設計の検体数との関係を示すこと
-・設計数量を超える場合はその扱いを協議すること</t>
+          <t>・発注者想定（2検体）との差について協議すること
+・151工区を1検体とする場合の代表性（各範囲の浚渫土量・土質）を示すこと</t>
         </is>
       </c>
       <c r="G10" s="10" t="n"/>
     </row>
-    <row r="11" ht="80" customHeight="1">
+    <row r="11" ht="95" customHeight="1">
       <c r="A11" s="7" t="n">
         <v>4</v>
       </c>
@@ -743,7 +746,7 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>位置図には採取箇所のみが示されており、採取深さ、混合試料の作り方、分析項目（土壌溶出量・含有量等）、受入先の基準が示されていない。試料が浚渫土を代表しているか判断するため、これらを示した採取計画が必要と考えられる。</t>
+          <t>位置図には採取箇所のみが示されており、採取深さ、試料の採取方法（単一試料か混合試料か）、分析項目（土壌溶出量・含有量等）、受入先の基準が示されていない。土砂条例施行規則第7条に基づく提出書類（試料採取位置図・現場写真、土壌調査資料採取報告書（第4号様式）、土壌分析結果証明書）に対応できる採取計画が必要と考えられる。</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
@@ -753,7 +756,7 @@
       </c>
       <c r="G11" s="10" t="n"/>
     </row>
-    <row r="12" ht="80" customHeight="1">
+    <row r="12" ht="95" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
           <t>総括所見</t>
@@ -762,8 +765,8 @@
       <c r="B12" s="3" t="n"/>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>本位置図では、151工区内に試料採取箇所を2箇所設ける理由が示されておらず、151工区の浚渫範囲も明示されていないため、採取箇所の妥当性を判断できない。
-受注者に対し、151工区の浚渫範囲の明示、採取箇所数の根拠、当初設計の検体数との関係、試料採取計画の提出を求め、その内容を確認したうえで採取に着手させることが望ましい。
+          <t>151工区の浚渫範囲は2つに分かれており、受注者は各範囲に1箇所ずつ（②・③）採取する計画（計3検体）であるが、2箇所とする根拠が示されていない。発注者は1箇所追加（①・③の計2検体）を想定しており、1検体の差がある。
+受注者に対し、151工区で2検体とする根拠（土砂条例・受入先の採取基準等）と、151工区の浚渫範囲・土量の明示を求め、根拠が認められない場合は、発注者想定の2検体（①・③）または②・③の混合試料による1検体とするよう協議することが望ましい。
 なお、試料採取前に確認を終えておく必要がある。</t>
         </is>
       </c>
